--- a/temp/espc-2/searchByMAC-2.xlsx
+++ b/temp/espc-2/searchByMAC-2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="41">
   <si>
     <t>ЭСПЦ-2</t>
   </si>
@@ -134,6 +134,9 @@
   </si>
   <si>
     <t>17.48</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
 </sst>
 </file>
@@ -490,7 +493,7 @@
     <col min="1" max="44" width="5.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -510,25 +513,40 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="F2" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
+      <c r="N2" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R2">
+        <v>7</v>
+      </c>
+      <c r="V2">
+        <v>8</v>
+      </c>
+      <c r="Z2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
         <v>1</v>
@@ -548,7 +566,7 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
@@ -570,7 +588,7 @@
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
@@ -592,7 +610,7 @@
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
@@ -614,7 +632,7 @@
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
@@ -636,7 +654,7 @@
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
@@ -658,7 +676,7 @@
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
@@ -680,7 +698,7 @@
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
@@ -702,7 +720,7 @@
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
@@ -724,7 +742,7 @@
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
@@ -746,7 +764,7 @@
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
@@ -768,7 +786,7 @@
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
@@ -790,7 +808,7 @@
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1" t="s">
@@ -812,7 +830,7 @@
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">

--- a/temp/espc-2/searchByMAC-2.xlsx
+++ b/temp/espc-2/searchByMAC-2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="47">
   <si>
     <t>ЭСПЦ-2</t>
   </si>
@@ -137,6 +137,24 @@
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>6.2.17</t>
+  </si>
+  <si>
+    <t>6.2.16</t>
+  </si>
+  <si>
+    <t>6.2.23</t>
+  </si>
+  <si>
+    <t>6.2.22</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
 </sst>
 </file>
@@ -487,13 +505,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB211"/>
+  <dimension ref="A1:AT211"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="44" width="5.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -513,7 +531,7 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -546,7 +564,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
         <v>1</v>
@@ -566,7 +584,7 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
@@ -576,19 +594,31 @@
         <v>3</v>
       </c>
       <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
+      <c r="F4">
+        <v>4</v>
+      </c>
       <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
+      <c r="L4" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="R4">
+        <v>6</v>
+      </c>
+      <c r="X4">
+        <v>7</v>
+      </c>
+      <c r="AE4">
+        <v>8</v>
+      </c>
+      <c r="AM4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
@@ -598,19 +628,51 @@
         <v>3</v>
       </c>
       <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
+      <c r="G5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
       <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
+      <c r="M5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="S5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U5" s="1"/>
+      <c r="Y5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA5" s="1"/>
+      <c r="AF5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH5" s="1"/>
+      <c r="AN5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AO5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP5" s="1"/>
+    </row>
+    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
@@ -620,19 +682,51 @@
         <v>3</v>
       </c>
       <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
+      <c r="G6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
       <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
+      <c r="M6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="S6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="U6" s="1"/>
+      <c r="Y6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA6" s="1"/>
+      <c r="AF6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH6" s="1"/>
+      <c r="AN6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AO6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AP6" s="1"/>
+    </row>
+    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
@@ -642,19 +736,51 @@
         <v>3</v>
       </c>
       <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
+      <c r="G7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
       <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
+      <c r="M7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="S7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="U7" s="1"/>
+      <c r="Y7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA7" s="1"/>
+      <c r="AF7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH7" s="1"/>
+      <c r="AN7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AO7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AP7" s="1"/>
+    </row>
+    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
@@ -664,19 +790,51 @@
         <v>3</v>
       </c>
       <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
+      <c r="G8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
       <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
+      <c r="M8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="S8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="U8" s="1"/>
+      <c r="Y8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA8" s="1"/>
+      <c r="AF8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH8" s="1"/>
+      <c r="AN8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AO8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AP8" s="1"/>
+    </row>
+    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
@@ -686,19 +844,51 @@
         <v>9</v>
       </c>
       <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
+      <c r="G9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="I9" s="1"/>
-      <c r="J9" s="2"/>
       <c r="K9" s="2"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
+      <c r="M9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="S9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U9" s="1"/>
+      <c r="Y9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA9" s="1"/>
+      <c r="AF9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH9" s="1"/>
+      <c r="AN9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AO9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP9" s="1"/>
+    </row>
+    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
@@ -708,19 +898,81 @@
         <v>11</v>
       </c>
       <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="2"/>
+      <c r="F10">
+        <v>11</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="K10" s="2"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="L10">
+        <v>11</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R10">
+        <v>11</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="X10">
+        <v>11</v>
+      </c>
+      <c r="Y10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AE10">
+        <v>11</v>
+      </c>
+      <c r="AF10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AM10">
+        <v>11</v>
+      </c>
+      <c r="AN10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP10" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
@@ -730,19 +982,61 @@
         <v>3</v>
       </c>
       <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
       <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="2"/>
+      <c r="H11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="K11" s="2"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="M11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AN11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP11" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
@@ -752,19 +1046,99 @@
         <v>3</v>
       </c>
       <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="2"/>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="K12" s="2"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="X12">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE12">
+        <v>1</v>
+      </c>
+      <c r="AF12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AG12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM12">
+        <v>1</v>
+      </c>
+      <c r="AN12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AO12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AQ12" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
@@ -774,19 +1148,99 @@
         <v>3</v>
       </c>
       <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="2"/>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="K13" s="2"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="X13">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE13">
+        <v>1</v>
+      </c>
+      <c r="AF13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM13">
+        <v>1</v>
+      </c>
+      <c r="AN13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AQ13" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
@@ -796,19 +1250,57 @@
         <v>3</v>
       </c>
       <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="2"/>
       <c r="K14" s="2"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="S14" s="1">
+        <v>6</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y14" s="1">
+        <v>6</v>
+      </c>
+      <c r="Z14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF14" s="1">
+        <v>6</v>
+      </c>
+      <c r="AG14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AN14" s="1">
+        <v>6</v>
+      </c>
+      <c r="AO14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ14" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1" t="s">
@@ -818,19 +1310,51 @@
         <v>3</v>
       </c>
       <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="2"/>
+      <c r="F15">
+        <v>4</v>
+      </c>
       <c r="K15" s="2"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="L15">
+        <v>5</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AO15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ15" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
@@ -840,37 +1364,126 @@
         <v>3</v>
       </c>
       <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
+      <c r="G16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="I16" s="1"/>
-      <c r="J16" s="2"/>
       <c r="K16" s="2"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
+      <c r="M16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="T16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AG16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AO16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ16" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
+      <c r="G17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="I17" s="1"/>
-      <c r="J17" s="2"/>
       <c r="K17" s="2"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
+      <c r="M17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Y17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AN17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AR17" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
         <v>8</v>
@@ -878,19 +1491,65 @@
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
+      <c r="G18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="I18" s="1"/>
-      <c r="J18" s="2"/>
       <c r="K18" s="2"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
+      <c r="M18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R18">
+        <v>6</v>
+      </c>
+      <c r="Y18" s="1"/>
+      <c r="Z18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF18" s="1"/>
+      <c r="AG18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN18" s="1"/>
+      <c r="AO18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AR18" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
@@ -900,19 +1559,66 @@
         <v>18</v>
       </c>
       <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
+      <c r="G19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="I19" s="1"/>
-      <c r="J19" s="2"/>
       <c r="K19" s="2"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
+      <c r="M19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U19" s="1"/>
+      <c r="AF19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AK19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AR19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AS19" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
@@ -922,19 +1628,65 @@
         <v>18</v>
       </c>
       <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
+      <c r="G20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="I20" s="1"/>
-      <c r="J20" s="2"/>
       <c r="K20" s="2"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
+      <c r="M20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="U20" s="1"/>
+      <c r="X20">
+        <v>7</v>
+      </c>
+      <c r="AF20" s="1"/>
+      <c r="AG20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AK20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN20" s="1"/>
+      <c r="AO20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AR20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AS20" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
@@ -944,19 +1696,53 @@
         <v>18</v>
       </c>
       <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
-      <c r="J21" s="2"/>
       <c r="K21" s="2"/>
-      <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="U21" s="1"/>
+      <c r="Y21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA21" s="1"/>
+      <c r="AM21">
+        <v>1</v>
+      </c>
+      <c r="AN21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AO21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AR21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AS21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT21" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1" t="s">
@@ -966,19 +1752,61 @@
         <v>18</v>
       </c>
       <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
       <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="2"/>
+      <c r="H22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="K22" s="2"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="U22" s="1"/>
+      <c r="Y22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA22" s="1"/>
+      <c r="AE22">
+        <v>8</v>
+      </c>
+      <c r="AN22" s="1"/>
+      <c r="AO22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AR22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AS22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT22" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
@@ -999,8 +1827,29 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U23" s="1"/>
+      <c r="Y23" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA23" s="1"/>
+      <c r="AF23" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH23" s="1"/>
+    </row>
+    <row r="24" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
@@ -1021,8 +1870,28 @@
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="1"/>
+      <c r="Y24" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z24" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA24" s="1"/>
+      <c r="AF24" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG24" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH24" s="1"/>
+      <c r="AM24">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1" t="s">
@@ -1043,8 +1912,38 @@
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y25" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA25" s="1"/>
+      <c r="AF25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH25" s="1"/>
+      <c r="AN25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AO25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP25" s="1"/>
+    </row>
+    <row r="26" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1" t="s">
@@ -1065,8 +1964,37 @@
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S26" s="1">
+        <v>6</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V26" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y26" s="1"/>
+      <c r="Z26" s="1"/>
+      <c r="AA26" s="1"/>
+      <c r="AF26" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG26" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH26" s="1"/>
+      <c r="AN26" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AO26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AP26" s="1"/>
+    </row>
+    <row r="27" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1" t="s">
@@ -1087,8 +2015,40 @@
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="T27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V27" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF27" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH27" s="1"/>
+      <c r="AN27" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AO27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AP27" s="1"/>
+    </row>
+    <row r="28" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1" t="s">
@@ -1109,8 +2069,39 @@
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="T28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y28" s="1">
+        <v>6</v>
+      </c>
+      <c r="Z28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB28" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF28" s="1"/>
+      <c r="AG28" s="1"/>
+      <c r="AH28" s="1"/>
+      <c r="AN28" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AO28" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AP28" s="1"/>
+    </row>
+    <row r="29" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1" t="s">
@@ -1131,8 +2122,33 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Z29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AN29" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AO29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP29" s="1"/>
+    </row>
+    <row r="30" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1" t="s">
@@ -1153,8 +2169,32 @@
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Z30" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB30" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF30" s="1">
+        <v>6</v>
+      </c>
+      <c r="AG30" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI30" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AN30" s="1"/>
+      <c r="AO30" s="1"/>
+      <c r="AP30" s="1"/>
+    </row>
+    <row r="31" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1" t="s">
@@ -1175,8 +2215,41 @@
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Y31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z31" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB31" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC31" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AG31" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AN31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO31" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP31" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1193,8 +2266,42 @@
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Y32" s="1"/>
+      <c r="Z32" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB32" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC32" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG32" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI32" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AN32" s="1">
+        <v>6</v>
+      </c>
+      <c r="AO32" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ32" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1" t="s">
         <v>17</v>
@@ -1217,8 +2324,32 @@
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="AF33" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ33" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AO33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ33" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1" t="s">
@@ -1247,8 +2378,30 @@
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="AF34" s="1"/>
+      <c r="AG34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH34" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI34" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ34" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP34" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ34" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1" t="s">
@@ -1277,8 +2430,41 @@
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="AF35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH35" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI35" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ35" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AK35" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP35" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ35" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AR35" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1" t="s">
@@ -1307,8 +2493,37 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="AF36" s="1"/>
+      <c r="AG36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH36" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI36" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ36" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AK36" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN36" s="1"/>
+      <c r="AO36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP36" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ36" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AR36" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1" t="s">
@@ -1329,8 +2544,26 @@
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="AN37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO37" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP37" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ37" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AR37" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AS37" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1" t="s">
@@ -1355,8 +2588,24 @@
       <c r="N38" s="1"/>
       <c r="O38" s="2"/>
       <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="AN38" s="1"/>
+      <c r="AO38" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP38" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ38" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AR38" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AS38" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1" t="s">
@@ -1385,8 +2634,15 @@
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="AN39" s="1"/>
+      <c r="AO39" s="1"/>
+      <c r="AP39" s="1"/>
+      <c r="AQ39" s="1"/>
+      <c r="AR39" s="1"/>
+      <c r="AS39" s="1"/>
+      <c r="AT39" s="1"/>
+    </row>
+    <row r="40" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1" t="s">
@@ -1407,8 +2663,27 @@
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="AN40" s="1"/>
+      <c r="AO40" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ40" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AR40" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AS40" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT40" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="41" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1" t="s">
@@ -1430,7 +2705,7 @@
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1" t="s">
@@ -1460,7 +2735,7 @@
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1" t="s">
@@ -1486,7 +2761,7 @@
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1" t="s">
@@ -1508,7 +2783,7 @@
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1" t="s">
@@ -1530,7 +2805,7 @@
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1" t="s">
@@ -1560,7 +2835,7 @@
       <c r="O46" s="1"/>
       <c r="P46" s="1"/>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -1578,7 +2853,7 @@
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1" t="s">
         <v>16</v>
